--- a/output/Data and Chart Outputs/china_nbs_fixed_asset_investment_monthly.xlsx
+++ b/output/Data and Chart Outputs/china_nbs_fixed_asset_investment_monthly.xlsx
@@ -158,7 +158,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China fixed investment by sector y/y (NBS) (to Aug/26)</a:t>
+              <a:t>China fixed investment by sector y/y (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$96</f>
+              <f>'Chart'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$96</f>
+              <f>'Chart'!$B$2:$B$97</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -230,12 +230,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$96</f>
+              <f>'Chart'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$96</f>
+              <f>'Chart'!$C$2:$C$97</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -266,12 +266,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$96</f>
+              <f>'Chart'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$96</f>
+              <f>'Chart'!$D$2:$D$97</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -302,12 +302,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$96</f>
+              <f>'Chart'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$96</f>
+              <f>'Chart'!$E$2:$E$97</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -340,8 +340,8 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="7"/>
-        <tickMarkSkip val="7"/>
+        <tickLblSkip val="8"/>
+        <tickMarkSkip val="8"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -407,7 +407,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China fixed investment by industry y/y (NBS) (to Aug/26)</a:t>
+              <a:t>China fixed investment by industry y/y (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -443,12 +443,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - fixed investment by ind'!$A$2:$A$96</f>
+              <f>'Chart - fixed investment by ind'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - fixed investment by ind'!$B$2:$B$96</f>
+              <f>'Chart - fixed investment by ind'!$B$2:$B$97</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - fixed investment by ind'!$A$2:$A$96</f>
+              <f>'Chart - fixed investment by ind'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - fixed investment by ind'!$C$2:$C$96</f>
+              <f>'Chart - fixed investment by ind'!$C$2:$C$97</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -515,12 +515,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - fixed investment by ind'!$A$2:$A$96</f>
+              <f>'Chart - fixed investment by ind'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - fixed investment by ind'!$D$2:$D$96</f>
+              <f>'Chart - fixed investment by ind'!$D$2:$D$97</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,8 +553,8 @@
         </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="7"/>
-        <tickMarkSkip val="7"/>
+        <tickLblSkip val="8"/>
+        <tickMarkSkip val="8"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1018,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2664,6 +2664,23 @@
       </c>
       <c r="E96" t="n">
         <v>-9.9</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B97" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="E97" t="n">
+        <v>-10</v>
       </c>
     </row>
   </sheetData>
@@ -2678,7 +2695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4034,6 +4051,20 @@
       </c>
       <c r="D96" t="n">
         <v>-6.9</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B97" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-6.8</v>
       </c>
     </row>
   </sheetData>
@@ -4048,7 +4079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX151"/>
+  <dimension ref="A1:AX152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19670,6 +19701,155 @@
       </c>
       <c r="AX151" t="n">
         <v>-0.5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B152" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="D152" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="E152" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F152" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G152" t="n">
+        <v>-12.1</v>
+      </c>
+      <c r="H152" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="I152" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="J152" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K152" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="L152" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M152" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="N152" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="O152" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="P152" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="R152" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="S152" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="T152" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="U152" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V152" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="W152" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="X152" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>-15.3</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>-17</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>33411.5</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>652.7</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>12974.3</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>19784.5</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>-26</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
